--- a/data/industry/CFM/SODIMM.xlsx
+++ b/data/industry/CFM/SODIMM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9A261DD-1C93-440B-9E22-3D694AD142B4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E60B4FF-7EEA-423D-86F5-ADC1F78A978E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -60,6 +60,9 @@
     <t>UTC+8</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>UTC+8</t>
+  </si>
 </sst>
 </file>
 
@@ -67,9 +70,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="181" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -132,35 +135,35 @@
   </cellStyleXfs>
   <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="181" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
@@ -442,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -1086,7 +1089,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E28" s="11">
         <v>35.5</v>
@@ -1095,6 +1098,121 @@
         <v>41.4</v>
       </c>
       <c r="G28" s="11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="11">
+        <v>35.5</v>
+      </c>
+      <c r="F29" s="11">
+        <v>41.4</v>
+      </c>
+      <c r="G29" s="11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="11">
+        <v>35.5</v>
+      </c>
+      <c r="F30" s="11">
+        <v>41.4</v>
+      </c>
+      <c r="G30" s="11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="11">
+        <v>35.5</v>
+      </c>
+      <c r="F31" s="11">
+        <v>41.4</v>
+      </c>
+      <c r="G31" s="11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="11">
+        <v>35.5</v>
+      </c>
+      <c r="F32" s="11">
+        <v>41.4</v>
+      </c>
+      <c r="G32" s="11">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="11">
+        <v>35.5</v>
+      </c>
+      <c r="F33" s="11">
+        <v>41.4</v>
+      </c>
+      <c r="G33" s="11">
         <v>38</v>
       </c>
     </row>
@@ -1106,7 +1224,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9F7D34-9614-456C-B66D-E33AF53643A7}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -1750,7 +1868,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E28" s="11">
         <v>65</v>
@@ -1760,6 +1878,121 @@
       </c>
       <c r="G28" s="11">
         <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="11">
+        <v>75</v>
+      </c>
+      <c r="F29" s="11">
+        <v>82</v>
+      </c>
+      <c r="G29" s="11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="11">
+        <v>75</v>
+      </c>
+      <c r="F30" s="11">
+        <v>82</v>
+      </c>
+      <c r="G30" s="11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="11">
+        <v>75</v>
+      </c>
+      <c r="F31" s="11">
+        <v>82</v>
+      </c>
+      <c r="G31" s="11">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="11">
+        <v>85</v>
+      </c>
+      <c r="F32" s="11">
+        <v>92</v>
+      </c>
+      <c r="G32" s="11">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="11">
+        <v>85</v>
+      </c>
+      <c r="F33" s="11">
+        <v>92</v>
+      </c>
+      <c r="G33" s="11">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1770,7 +2003,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA0A4F0-C10D-4632-99CA-14E155280997}">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -2414,7 +2647,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E28" s="11">
         <v>175</v>
@@ -2423,6 +2656,121 @@
         <v>182</v>
       </c>
       <c r="G28" s="11">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="B29" s="8">
+        <v>46056</v>
+      </c>
+      <c r="C29" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="11">
+        <v>175</v>
+      </c>
+      <c r="F29" s="11">
+        <v>182</v>
+      </c>
+      <c r="G29" s="11">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="B30" s="8">
+        <v>46063</v>
+      </c>
+      <c r="C30" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="11">
+        <v>175</v>
+      </c>
+      <c r="F30" s="11">
+        <v>182</v>
+      </c>
+      <c r="G30" s="11">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="B31" s="8">
+        <v>46077</v>
+      </c>
+      <c r="C31" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="11">
+        <v>175</v>
+      </c>
+      <c r="F31" s="11">
+        <v>182</v>
+      </c>
+      <c r="G31" s="11">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="B32" s="8">
+        <v>46084</v>
+      </c>
+      <c r="C32" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="11">
+        <v>175</v>
+      </c>
+      <c r="F32" s="11">
+        <v>182</v>
+      </c>
+      <c r="G32" s="11">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="8">
+        <v>46091</v>
+      </c>
+      <c r="C33" s="6">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="11">
+        <v>175</v>
+      </c>
+      <c r="F33" s="11">
+        <v>182</v>
+      </c>
+      <c r="G33" s="11">
         <v>180</v>
       </c>
     </row>

--- a/data/industry/CFM/SODIMM.xlsx
+++ b/data/industry/CFM/SODIMM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E60B4FF-7EEA-423D-86F5-ADC1F78A978E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD7B3FA4-072C-4D10-BBEB-42AD7549E79E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -445,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -1216,6 +1216,52 @@
         <v>38</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="11">
+        <v>39.5</v>
+      </c>
+      <c r="F34" s="11">
+        <v>45.4</v>
+      </c>
+      <c r="G34" s="11">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="11">
+        <v>39.5</v>
+      </c>
+      <c r="F35" s="11">
+        <v>45.4</v>
+      </c>
+      <c r="G35" s="11">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1224,7 +1270,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9F7D34-9614-456C-B66D-E33AF53643A7}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -1995,6 +2041,52 @@
         <v>90</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="11">
+        <v>91</v>
+      </c>
+      <c r="F34" s="11">
+        <v>98</v>
+      </c>
+      <c r="G34" s="11">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="11">
+        <v>91</v>
+      </c>
+      <c r="F35" s="11">
+        <v>98</v>
+      </c>
+      <c r="G35" s="11">
+        <v>96</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2003,7 +2095,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA0A4F0-C10D-4632-99CA-14E155280997}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.75" style="8" bestFit="1" customWidth="1"/>
@@ -2774,6 +2866,52 @@
         <v>180</v>
       </c>
     </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="B34" s="8">
+        <v>46098</v>
+      </c>
+      <c r="C34" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="11">
+        <v>195</v>
+      </c>
+      <c r="F34" s="11">
+        <v>202</v>
+      </c>
+      <c r="G34" s="11">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="B35" s="8">
+        <v>46105</v>
+      </c>
+      <c r="C35" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="11">
+        <v>195</v>
+      </c>
+      <c r="F35" s="11">
+        <v>202</v>
+      </c>
+      <c r="G35" s="11">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/industry/CFM/SODIMM.xlsx
+++ b/data/industry/CFM/SODIMM.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5CD5A0C-6ECA-40D7-A97D-8FFAEC4C86D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1BE2C08-1AB3-4E2C-BCF8-779134C804E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DDR4 SODIMM 4GB 3200" sheetId="1" r:id="rId1"/>
     <sheet name="DDR4 SODIMM 8GB 3200" sheetId="2" r:id="rId2"/>
     <sheet name="DDR4 SODIMM 16GB 3200" sheetId="3" r:id="rId3"/>
+    <sheet name="DDR5 SODIMM 8GB 5600" sheetId="4" r:id="rId4"/>
+    <sheet name="DDR5 SODIMM 16GB 5600" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="9">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -68,24 +70,26 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+  <numFmts count="6">
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -98,7 +102,7 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -108,6 +112,14 @@
       <color theme="1"/>
       <name val="Verdana"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -127,52 +139,78 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="쉼표" xfId="2" builtinId="3"/>
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -452,19 +490,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -487,7 +525,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45860</v>
       </c>
@@ -510,7 +548,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -533,7 +571,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -556,7 +594,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45881</v>
       </c>
@@ -579,7 +617,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45888</v>
       </c>
@@ -602,7 +640,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45895</v>
       </c>
@@ -625,7 +663,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45902</v>
       </c>
@@ -648,7 +686,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45909</v>
       </c>
@@ -671,7 +709,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45916</v>
       </c>
@@ -694,7 +732,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45923</v>
       </c>
@@ -717,7 +755,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45930</v>
       </c>
@@ -740,7 +778,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45944</v>
       </c>
@@ -763,7 +801,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45951</v>
       </c>
@@ -786,7 +824,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45958</v>
       </c>
@@ -809,7 +847,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45965</v>
       </c>
@@ -832,7 +870,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45972</v>
       </c>
@@ -855,7 +893,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45979</v>
       </c>
@@ -878,7 +916,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45986</v>
       </c>
@@ -901,7 +939,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45993</v>
       </c>
@@ -924,7 +962,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>46000</v>
       </c>
@@ -947,7 +985,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>46007</v>
       </c>
@@ -970,7 +1008,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>46014</v>
       </c>
@@ -993,7 +1031,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>46021</v>
       </c>
@@ -1016,7 +1054,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>46028</v>
       </c>
@@ -1039,7 +1077,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="8">
         <v>46035</v>
       </c>
@@ -1062,7 +1100,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="8">
         <v>46042</v>
       </c>
@@ -1085,7 +1123,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="5">
         <v>46049</v>
       </c>
@@ -1108,7 +1146,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="8">
         <v>46056</v>
       </c>
@@ -1131,7 +1169,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="8">
         <v>46063</v>
       </c>
@@ -1154,7 +1192,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="8">
         <v>46077</v>
       </c>
@@ -1177,7 +1215,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="8">
         <v>46084</v>
       </c>
@@ -1200,7 +1238,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="8">
         <v>46091</v>
       </c>
@@ -1223,7 +1261,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="8">
         <v>46098</v>
       </c>
@@ -1246,7 +1284,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="8">
         <v>46105</v>
       </c>
@@ -1269,7 +1307,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="8">
         <v>46112</v>
       </c>
@@ -1292,7 +1330,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="8">
         <v>46119</v>
       </c>
@@ -1315,7 +1353,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="8">
         <v>46126</v>
       </c>
@@ -1338,7 +1376,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="8">
         <v>46133</v>
       </c>
@@ -1360,6 +1398,51 @@
       <c r="G39" s="11">
         <v>42</v>
       </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
+      <c r="C41" s="4"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
+      <c r="G41" s="4"/>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
+      <c r="C42" s="4"/>
+      <c r="D42" s="4"/>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
+      <c r="G42" s="4"/>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="4"/>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="4"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
@@ -1369,19 +1452,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D9F7D34-9614-456C-B66D-E33AF53643A7}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="14"/>
-    <col min="7" max="7" width="11.19921875" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1404,7 +1487,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45860</v>
       </c>
@@ -1427,7 +1510,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -1450,7 +1533,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -1473,7 +1556,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45881</v>
       </c>
@@ -1496,7 +1579,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45888</v>
       </c>
@@ -1519,7 +1602,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45895</v>
       </c>
@@ -1542,7 +1625,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45902</v>
       </c>
@@ -1565,7 +1648,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45909</v>
       </c>
@@ -1588,7 +1671,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45916</v>
       </c>
@@ -1611,7 +1694,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45923</v>
       </c>
@@ -1634,7 +1717,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45930</v>
       </c>
@@ -1657,7 +1740,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45944</v>
       </c>
@@ -1680,7 +1763,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45951</v>
       </c>
@@ -1703,7 +1786,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45958</v>
       </c>
@@ -1726,7 +1809,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45965</v>
       </c>
@@ -1749,7 +1832,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45972</v>
       </c>
@@ -1772,7 +1855,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45979</v>
       </c>
@@ -1795,7 +1878,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45986</v>
       </c>
@@ -1818,7 +1901,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45993</v>
       </c>
@@ -1841,7 +1924,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>46000</v>
       </c>
@@ -1864,7 +1947,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>46007</v>
       </c>
@@ -1887,7 +1970,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>46014</v>
       </c>
@@ -1910,7 +1993,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>46021</v>
       </c>
@@ -1933,7 +2016,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>46028</v>
       </c>
@@ -1956,7 +2039,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="8">
         <v>46035</v>
       </c>
@@ -1979,7 +2062,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="8">
         <v>46042</v>
       </c>
@@ -2002,7 +2085,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="8">
         <v>46049</v>
       </c>
@@ -2025,7 +2108,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="8">
         <v>46056</v>
       </c>
@@ -2048,7 +2131,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="8">
         <v>46063</v>
       </c>
@@ -2071,7 +2154,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="8">
         <v>46077</v>
       </c>
@@ -2094,7 +2177,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="8">
         <v>46084</v>
       </c>
@@ -2117,7 +2200,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="8">
         <v>46091</v>
       </c>
@@ -2140,7 +2223,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="8">
         <v>46098</v>
       </c>
@@ -2163,7 +2246,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="8">
         <v>46105</v>
       </c>
@@ -2186,7 +2269,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="8">
         <v>46112</v>
       </c>
@@ -2209,7 +2292,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="8">
         <v>46119</v>
       </c>
@@ -2232,7 +2315,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="8">
         <v>46126</v>
       </c>
@@ -2255,7 +2338,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="8">
         <v>46133</v>
       </c>
@@ -2276,6 +2359,144 @@
       </c>
       <c r="G39" s="14">
         <v>90</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="15">
+        <v>80</v>
+      </c>
+      <c r="F40" s="15">
+        <v>87</v>
+      </c>
+      <c r="G40" s="15">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="15">
+        <v>77</v>
+      </c>
+      <c r="F41" s="15">
+        <v>84</v>
+      </c>
+      <c r="G41" s="15">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="15">
+        <v>75</v>
+      </c>
+      <c r="F42" s="15">
+        <v>82</v>
+      </c>
+      <c r="G42" s="15">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="15">
+        <v>65</v>
+      </c>
+      <c r="F43" s="15">
+        <v>72</v>
+      </c>
+      <c r="G43" s="15">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="15">
+        <v>65</v>
+      </c>
+      <c r="F44" s="15">
+        <v>72</v>
+      </c>
+      <c r="G44" s="15">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="15">
+        <v>65</v>
+      </c>
+      <c r="F45" s="15">
+        <v>72</v>
+      </c>
+      <c r="G45" s="15">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -2286,19 +2507,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EA0A4F0-C10D-4632-99CA-14E155280997}">
-  <dimension ref="A1:G39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:G45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="1" width="12.69921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.19921875" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.6640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="7" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" style="11"/>
-    <col min="7" max="7" width="11.19921875" style="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.21875" style="11" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2321,7 +2542,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>45860</v>
       </c>
@@ -2344,7 +2565,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7">
       <c r="A3" s="5">
         <v>45867</v>
       </c>
@@ -2367,7 +2588,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7">
       <c r="A4" s="5">
         <v>45874</v>
       </c>
@@ -2390,7 +2611,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>45881</v>
       </c>
@@ -2413,7 +2634,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>45888</v>
       </c>
@@ -2436,7 +2657,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>45895</v>
       </c>
@@ -2459,7 +2680,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7">
       <c r="A8" s="5">
         <v>45902</v>
       </c>
@@ -2482,7 +2703,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7">
       <c r="A9" s="5">
         <v>45909</v>
       </c>
@@ -2505,7 +2726,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7">
       <c r="A10" s="5">
         <v>45916</v>
       </c>
@@ -2528,7 +2749,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7">
       <c r="A11" s="5">
         <v>45923</v>
       </c>
@@ -2551,7 +2772,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7">
       <c r="A12" s="5">
         <v>45930</v>
       </c>
@@ -2574,7 +2795,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7">
       <c r="A13" s="5">
         <v>45944</v>
       </c>
@@ -2597,7 +2818,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7">
       <c r="A14" s="5">
         <v>45951</v>
       </c>
@@ -2620,7 +2841,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7">
       <c r="A15" s="5">
         <v>45958</v>
       </c>
@@ -2643,7 +2864,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7">
       <c r="A16" s="5">
         <v>45965</v>
       </c>
@@ -2666,7 +2887,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7">
       <c r="A17" s="5">
         <v>45972</v>
       </c>
@@ -2689,7 +2910,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7">
       <c r="A18" s="5">
         <v>45979</v>
       </c>
@@ -2712,7 +2933,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7">
       <c r="A19" s="5">
         <v>45986</v>
       </c>
@@ -2735,7 +2956,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7">
       <c r="A20" s="5">
         <v>45993</v>
       </c>
@@ -2758,7 +2979,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7">
       <c r="A21" s="5">
         <v>46000</v>
       </c>
@@ -2781,7 +3002,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>46007</v>
       </c>
@@ -2804,7 +3025,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7">
       <c r="A23" s="5">
         <v>46014</v>
       </c>
@@ -2827,7 +3048,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7">
       <c r="A24" s="5">
         <v>46021</v>
       </c>
@@ -2850,7 +3071,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7">
       <c r="A25" s="5">
         <v>46028</v>
       </c>
@@ -2873,7 +3094,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7">
       <c r="A26" s="8">
         <v>46035</v>
       </c>
@@ -2896,7 +3117,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7">
       <c r="A27" s="8">
         <v>46042</v>
       </c>
@@ -2919,7 +3140,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7">
       <c r="A28" s="8">
         <v>46049</v>
       </c>
@@ -2942,7 +3163,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7">
       <c r="A29" s="8">
         <v>46056</v>
       </c>
@@ -2965,7 +3186,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7">
       <c r="A30" s="8">
         <v>46063</v>
       </c>
@@ -2988,7 +3209,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7">
       <c r="A31" s="8">
         <v>46077</v>
       </c>
@@ -3011,7 +3232,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7">
       <c r="A32" s="8">
         <v>46084</v>
       </c>
@@ -3034,7 +3255,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7">
       <c r="A33" s="8">
         <v>46091</v>
       </c>
@@ -3057,7 +3278,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7">
       <c r="A34" s="8">
         <v>46098</v>
       </c>
@@ -3080,7 +3301,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7">
       <c r="A35" s="8">
         <v>46105</v>
       </c>
@@ -3103,7 +3324,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7">
       <c r="A36" s="8">
         <v>46112</v>
       </c>
@@ -3126,7 +3347,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7">
       <c r="A37" s="8">
         <v>46119</v>
       </c>
@@ -3149,7 +3370,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7">
       <c r="A38" s="8">
         <v>46126</v>
       </c>
@@ -3172,7 +3393,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7">
       <c r="A39" s="8">
         <v>46133</v>
       </c>
@@ -3193,10 +3414,416 @@
       </c>
       <c r="G39" s="11">
         <v>190</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="B40" s="8">
+        <v>46140</v>
+      </c>
+      <c r="C40" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="11">
+        <v>175</v>
+      </c>
+      <c r="F40" s="11">
+        <v>182</v>
+      </c>
+      <c r="G40" s="11">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="B41" s="8">
+        <v>46154</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="11">
+        <v>175</v>
+      </c>
+      <c r="F41" s="11">
+        <v>182</v>
+      </c>
+      <c r="G41" s="11">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="B42" s="8">
+        <v>46161</v>
+      </c>
+      <c r="C42" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="11">
+        <v>160</v>
+      </c>
+      <c r="F42" s="11">
+        <v>180</v>
+      </c>
+      <c r="G42" s="11">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="B43" s="8">
+        <v>46168</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="11">
+        <v>145</v>
+      </c>
+      <c r="F43" s="11">
+        <v>165</v>
+      </c>
+      <c r="G43" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="B44" s="8">
+        <v>46175</v>
+      </c>
+      <c r="C44" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="11">
+        <v>145</v>
+      </c>
+      <c r="F44" s="11">
+        <v>165</v>
+      </c>
+      <c r="G44" s="11">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46182</v>
+      </c>
+      <c r="C45" s="6">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="11">
+        <v>145</v>
+      </c>
+      <c r="F45" s="11">
+        <v>165</v>
+      </c>
+      <c r="G45" s="11">
+        <v>155</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5297F85F-0123-4AD4-9FF2-92367D502EFD}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.5546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="21">
+        <v>46161</v>
+      </c>
+      <c r="B2" s="21">
+        <v>46161</v>
+      </c>
+      <c r="C2" s="22">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="24">
+        <v>105</v>
+      </c>
+      <c r="F2" s="24">
+        <v>120</v>
+      </c>
+      <c r="G2" s="24">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="21">
+        <v>46168</v>
+      </c>
+      <c r="B3" s="21">
+        <v>46168</v>
+      </c>
+      <c r="C3" s="22">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="24">
+        <v>105</v>
+      </c>
+      <c r="F3" s="24">
+        <v>120</v>
+      </c>
+      <c r="G3" s="24">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="21">
+        <v>46175</v>
+      </c>
+      <c r="B4" s="21">
+        <v>46175</v>
+      </c>
+      <c r="C4" s="22">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="24">
+        <v>105</v>
+      </c>
+      <c r="F4" s="24">
+        <v>120</v>
+      </c>
+      <c r="G4" s="24">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="21">
+        <v>46182</v>
+      </c>
+      <c r="B5" s="21">
+        <v>46182</v>
+      </c>
+      <c r="C5" s="22">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="24">
+        <v>105</v>
+      </c>
+      <c r="F5" s="24">
+        <v>120</v>
+      </c>
+      <c r="G5" s="24">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E39172B4-D2A0-49CA-B32F-E92273A8EC79}">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="12.6640625" style="21" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" style="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.77734375" style="22" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="9.5546875" style="24" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.33203125" style="24" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="21">
+        <v>46161</v>
+      </c>
+      <c r="B2" s="21">
+        <v>46161</v>
+      </c>
+      <c r="C2" s="22">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="24">
+        <v>220</v>
+      </c>
+      <c r="F2" s="24">
+        <v>240</v>
+      </c>
+      <c r="G2" s="24">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="21">
+        <v>46168</v>
+      </c>
+      <c r="B3" s="21">
+        <v>46168</v>
+      </c>
+      <c r="C3" s="22">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="24">
+        <v>220</v>
+      </c>
+      <c r="F3" s="24">
+        <v>240</v>
+      </c>
+      <c r="G3" s="24">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="21">
+        <v>46175</v>
+      </c>
+      <c r="B4" s="21">
+        <v>46175</v>
+      </c>
+      <c r="C4" s="22">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="24">
+        <v>220</v>
+      </c>
+      <c r="F4" s="24">
+        <v>240</v>
+      </c>
+      <c r="G4" s="24">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="21">
+        <v>46182</v>
+      </c>
+      <c r="B5" s="21">
+        <v>46182</v>
+      </c>
+      <c r="C5" s="22">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="24">
+        <v>220</v>
+      </c>
+      <c r="F5" s="24">
+        <v>240</v>
+      </c>
+      <c r="G5" s="24">
+        <v>230</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>